--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.32670005442683</v>
+        <v>6.22808875884436</v>
       </c>
       <c r="D2" t="n">
-        <v>38.2836110090995</v>
+        <v>6.22108678897867</v>
       </c>
       <c r="E2" t="n">
-        <v>16.91759095888086</v>
+        <v>2.74910853081814</v>
       </c>
       <c r="F2" t="n">
-        <v>16.90025621075459</v>
+        <v>2.746291634247621</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.16188197218855</v>
+        <v>11.72630582048064</v>
       </c>
       <c r="D3" t="n">
-        <v>72.08412343060868</v>
+        <v>11.71367005747391</v>
       </c>
       <c r="E3" t="n">
-        <v>16.91759095888086</v>
+        <v>2.74910853081814</v>
       </c>
       <c r="F3" t="n">
-        <v>16.90025621075459</v>
+        <v>2.746291634247621</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
